--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno2/anno2_task1_empathetic_engagement.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno2/anno2_task1_empathetic_engagement.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64950A7C-AEB6-4A8B-9D58-9DBA68328791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AF42DC-AB8C-471A-B55C-DFA349A7E0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,46 +56,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000132-0001</t>
-  </si>
-  <si>
-    <t>I'm considering an adventure trip to Patagonia.</t>
-  </si>
-  <si>
-    <t>That sounds like an amazing experience!</t>
-  </si>
-  <si>
-    <t>Patagonia sounds like an incredible adventure!</t>
-  </si>
-  <si>
-    <t>That sounds like an incredible adventure!</t>
-  </si>
-  <si>
-    <t>Patagonia is a breathtaking destination!</t>
-  </si>
-  <si>
-    <t>That's an exciting choice!</t>
-  </si>
-  <si>
-    <t>SFTANNO-000107-0001</t>
-  </si>
-  <si>
-    <t>It's so cloudy out, I don't even want to leave my house.</t>
-  </si>
-  <si>
-    <t>I hear you, sometimes it feels like there's no end in sight.</t>
-  </si>
-  <si>
-    <t>I feel the same way, it's hard to be motivated when it's so gloomy.</t>
-  </si>
-  <si>
-    <t>I get it, the clouds can be so depressing sometimes.</t>
-  </si>
-  <si>
-    <t>I feel the same way, it's so hard to motivate myself when it's this dark outside.</t>
-  </si>
-  <si>
-    <t>I know, it can be really discouraging to want to stay inside.</t>
+    <t>SFTANNO-000077-0001</t>
+  </si>
+  <si>
+    <t>I didn't know there were so many different regions and cultures in Japan.</t>
+  </si>
+  <si>
+    <t>Yes, it's a diverse country with many different regions and cultures.</t>
+  </si>
+  <si>
+    <t>It's true, each region has its own unique culture and customs.</t>
+  </si>
+  <si>
+    <t>Yes, Japan is incredibly diverse and there's so much to discover.</t>
+  </si>
+  <si>
+    <t>Yes, it's a diverse country with many different customs and traditions.</t>
+  </si>
+  <si>
+    <t>Yes, it's a very diverse country.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000153-0001</t>
+  </si>
+  <si>
+    <t>I'm worried my scrapbook won't be as good as some of the ones I've seen online.</t>
+  </si>
+  <si>
+    <t>I understand, it's natural to compare yourself to others.</t>
+  </si>
+  <si>
+    <t>It's natural to compare yourself to others, but remember that scrapbooking is a personal and unique art form.</t>
+  </si>
+  <si>
+    <t>It's normal to feel that way, but remember, scrapbooking is about capturing your memories, not about being perfect.</t>
+  </si>
+  <si>
+    <t>It's natural to compare your work to others, but remember, it's your unique style that makes it special.</t>
+  </si>
+  <si>
+    <t>It's normal to feel that way, but remember that scrapbooking is about the memories and the process, not just the end result.</t>
   </si>
   <si>
     <t>SFTANNO-000019-0001</t>
@@ -161,46 +161,46 @@
     <t>That's so sad to hear. It's like they don't care about the most vulnerable.</t>
   </si>
   <si>
-    <t>SFTANNO-000094-0001</t>
-  </si>
-  <si>
-    <t>Actually, I always opt for middle seats. Fewer distractions around me.</t>
-  </si>
-  <si>
-    <t>I never thought about that before.</t>
-  </si>
-  <si>
-    <t>Really? I can't imagine sitting in the middle seat.</t>
-  </si>
-  <si>
-    <t>Really? I've never tried that before.</t>
-  </si>
-  <si>
-    <t>Really? I could never imagine choosing a middle seat.</t>
-  </si>
-  <si>
-    <t>That's a unique choice!</t>
-  </si>
-  <si>
-    <t>SFTANNO-000103-0001</t>
-  </si>
-  <si>
-    <t>I've been browsing, but I don't want to compromise on quality either.</t>
-  </si>
-  <si>
-    <t>That's a tricky balance to find.</t>
-  </si>
-  <si>
-    <t>It's important to find the right fit.</t>
-  </si>
-  <si>
-    <t>That's a good point, you should only invest in something that meets your standards.</t>
-  </si>
-  <si>
-    <t>It's important to find the right balance between quality and price.</t>
-  </si>
-  <si>
-    <t>It's important to find a balance between quality and affordability.</t>
+    <t>SFTANNO-000131-0001</t>
+  </si>
+  <si>
+    <t>I've always dreamed of visiting Japan, but I'm afraid of the language barrier.</t>
+  </si>
+  <si>
+    <t>I can understand your concern.</t>
+  </si>
+  <si>
+    <t>I can understand the apprehension.</t>
+  </si>
+  <si>
+    <t>Japan is a fascinating country, but language can be a challenge.</t>
+  </si>
+  <si>
+    <t>It's a unique and fascinating country.</t>
+  </si>
+  <si>
+    <t>Japan is a beautiful country.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000058-0001</t>
+  </si>
+  <si>
+    <t>I heard a rumor that the COVID-19 vaccine makes you infertile, is that true?</t>
+  </si>
+  <si>
+    <t>No, that's a false claim, and it's been debunked by scientists.</t>
+  </si>
+  <si>
+    <t>That's a myth that has been debunked by experts.</t>
+  </si>
+  <si>
+    <t>No, that's a myth with no scientific basis. The vaccine is safe for all adults.</t>
+  </si>
+  <si>
+    <t>No, that's a myth. The vaccine doesn't affect fertility in any way.</t>
+  </si>
+  <si>
+    <t>No, that's not true. The vaccine has gone through extensive testing and has been proven safe.</t>
   </si>
   <si>
     <t>SFTANNO-000025-0001</t>
@@ -224,151 +224,151 @@
     <t>That's a great idea.</t>
   </si>
   <si>
-    <t>SFTANNO-000064-0001</t>
-  </si>
-  <si>
-    <t>I think we should reach out to local organizations and get involved in promoting change.</t>
-  </si>
-  <si>
-    <t>That's a great idea, it's important to use our voices and make our presence known.</t>
-  </si>
-  <si>
-    <t>That's a great idea. We can work together to make a positive impact.</t>
-  </si>
-  <si>
-    <t>That's a great idea, it's important to support local initiatives.</t>
-  </si>
-  <si>
-    <t>That's a great idea, we can work together to create a positive impact.</t>
-  </si>
-  <si>
-    <t>That's a great idea. We can also use social media to spread awareness and encourage others to take action.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000145-0001</t>
-  </si>
-  <si>
-    <t>That's a great idea! I hadn't thought about that.</t>
-  </si>
-  <si>
-    <t>I'm so glad I could help! Let's make a difference together.</t>
-  </si>
-  <si>
-    <t>I'm glad I could help! Every little bit helps!</t>
-  </si>
-  <si>
-    <t>It's a great way to learn from others and get support.</t>
-  </si>
-  <si>
-    <t>I'm glad I could help! There are so many ways to get involved and make a difference.</t>
-  </si>
-  <si>
-    <t>It's always good to have a support system when making changes towards sustainability.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000152-0001</t>
-  </si>
-  <si>
-    <t>I'm worried I won't be able to make anything as beautiful as the examples I've seen.</t>
-  </si>
-  <si>
-    <t>It's normal to feel that way, but don't worry, it takes practice.</t>
-  </si>
-  <si>
-    <t>I understand, but remember that everyone starts somewhere.</t>
-  </si>
-  <si>
-    <t>It's normal to feel that way, but it's important to remember that it's about the memories, not the aesthetic.</t>
-  </si>
-  <si>
-    <t>It's normal to feel that way, but you'll get the hang of it.</t>
-  </si>
-  <si>
-    <t>I understand how you feel, but remember, it's all about practice.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000159-0001</t>
-  </si>
-  <si>
-    <t>We should start by setting some ground rules for respectful discussion.</t>
-  </si>
-  <si>
-    <t>That's a great idea, we can work on that.</t>
-  </si>
-  <si>
-    <t>Agreed, we need boundaries to prevent future conflicts.</t>
-  </si>
-  <si>
-    <t>Agreed, we need to establish boundaries.</t>
-  </si>
-  <si>
-    <t>I agree, we need to show each other respect.</t>
-  </si>
-  <si>
-    <t>Agreed, let's make sure we listen and respect each other's opinions.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000096-0001</t>
-  </si>
-  <si>
-    <t>I missed the last train, and I'm stuck in the city.</t>
-  </si>
-  <si>
-    <t>Oh no, that's really inconvenient.</t>
-  </si>
-  <si>
-    <t>Oh no, that's a scary situation.</t>
-  </si>
-  <si>
-    <t>Oh no, that's awful. Are you okay?</t>
-  </si>
-  <si>
-    <t>That's really scary, especially in an unfamiliar place.</t>
-  </si>
-  <si>
-    <t>That's scary, are you okay?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000089-0001</t>
-  </si>
-  <si>
-    <t>They have a really solid defense and excellent ball control.</t>
-  </si>
-  <si>
-    <t>Yeah, but they can be quite predictable at times.</t>
-  </si>
-  <si>
-    <t>Yeah, they're hard to beat.</t>
-  </si>
-  <si>
-    <t>It's impressive to see a team that good.</t>
-  </si>
-  <si>
-    <t>I agree, but sometimes their offense can be too predictable.</t>
-  </si>
-  <si>
-    <t>Yeah, they're really good.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000135-0001</t>
-  </si>
-  <si>
-    <t>I did a river rafting trip once, but the water was so dirty.</t>
-  </si>
-  <si>
-    <t>I can understand why that would be unpleasant.</t>
-  </si>
-  <si>
-    <t>That sounds awful, I hate the idea of rafting in dirty water.</t>
-  </si>
-  <si>
-    <t>That's not ideal, but there are plenty of other adventures to choose from.</t>
-  </si>
-  <si>
-    <t>That sounds awful, I couldn't imagine rafting in dirty water.</t>
-  </si>
-  <si>
-    <t>That sounds gross.</t>
+    <t>SFTANNO-000098-0001</t>
+  </si>
+  <si>
+    <t>Have you ever ridden in an autonomous vehicle before?</t>
+  </si>
+  <si>
+    <t>No, I haven't had the chance yet.</t>
+  </si>
+  <si>
+    <t>No, but I'm curious to try it out sometime.</t>
+  </si>
+  <si>
+    <t>Yes, I have. It was a really smooth ride.</t>
+  </si>
+  <si>
+    <t>No, I haven't had the chance to yet.</t>
+  </si>
+  <si>
+    <t>No, I haven't.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000050-0001</t>
+  </si>
+  <si>
+    <t>I'm open to anything at this point.</t>
+  </si>
+  <si>
+    <t>That's great!</t>
+  </si>
+  <si>
+    <t>That's a good attitude to have.</t>
+  </si>
+  <si>
+    <t>That's the right attitude.</t>
+  </si>
+  <si>
+    <t>That's a great attitude to have.</t>
+  </si>
+  <si>
+    <t>That's the spirit!</t>
+  </si>
+  <si>
+    <t>SFTANNO-000078-0001</t>
+  </si>
+  <si>
+    <t>I'm worried about cultural misunderstandings when I visit my parents' homeland.</t>
+  </si>
+  <si>
+    <t>It's natural to have concerns about cultural differences, but they can also lead to rich experiences and learning.</t>
+  </si>
+  <si>
+    <t>It's natural to worry about cultural differences, but with some research and preparation, you can have a great experience.</t>
+  </si>
+  <si>
+    <t>That's a valid concern, but it's important to remember that cultural differences are a natural part of any travel experience.</t>
+  </si>
+  <si>
+    <t>It's normal to have those concerns, but remember that everyone is different and that cultural differences can be enriching.</t>
+  </si>
+  <si>
+    <t>It's natural to have concerns, but with proper research and an open mind, you can have a positive experience.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000095-0001</t>
+  </si>
+  <si>
+    <t>Yes, I have. I was so frustrated that the seat was uncomfortable and the entertainment system was broken.</t>
+  </si>
+  <si>
+    <t>That's terrible. I hate when that happens.</t>
+  </si>
+  <si>
+    <t>Ugh, I hate when that happens. It can really ruin the experience.</t>
+  </si>
+  <si>
+    <t>That's terrible! I hate when the entertainment system isn't working.</t>
+  </si>
+  <si>
+    <t>That sounds terrible. It's unacceptable when airlines don't prioritize customer satisfaction.</t>
+  </si>
+  <si>
+    <t>That's so annoying! I've had similar experiences.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000139-0001</t>
+  </si>
+  <si>
+    <t>I'm scared my children are spending too much time online.</t>
+  </si>
+  <si>
+    <t>It's important to monitor their online activity and set boundaries.</t>
+  </si>
+  <si>
+    <t>It's a valid concern, there are so many risks.</t>
+  </si>
+  <si>
+    <t>It's a valid concern, especially with all the dangers online.</t>
+  </si>
+  <si>
+    <t>It's a valid concern, especially with all the content out there.</t>
+  </si>
+  <si>
+    <t>It's important to monitor their online activity.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000130-0001</t>
+  </si>
+  <si>
+    <t>One episode covered the injustices faced by indigenous communities in regard to traditional plant knowledge and genetics research.</t>
+  </si>
+  <si>
+    <t>That's a frustrating and complicated issue.</t>
+  </si>
+  <si>
+    <t>That's a really important issue that needs to be addressed.</t>
+  </si>
+  <si>
+    <t>That's a terrible situation.</t>
+  </si>
+  <si>
+    <t>That's upsetting to hear.</t>
+  </si>
+  <si>
+    <t>That's a serious issue that needs to be addressed.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000073-0001</t>
+  </si>
+  <si>
+    <t>I saw a video of a robot dancing and it was just strange to watch.</t>
+  </si>
+  <si>
+    <t>I agree, it's not really human-like movement.</t>
+  </si>
+  <si>
+    <t>I can imagine. Robots are just not meant to dance.</t>
+  </si>
+  <si>
+    <t>I can imagine. It's almost like they're taking away the uniqueness of human dance.</t>
+  </si>
+  <si>
+    <t>I agree, it's kind of unsettling to see robots mimicking human behavior.</t>
+  </si>
+  <si>
+    <t>I can imagine. It's not something I'd want to watch either.</t>
   </si>
   <si>
     <t>SFTANNO-000018-0001</t>
@@ -392,46 +392,46 @@
     <t>It is incredible, isn't it?</t>
   </si>
   <si>
-    <t>SFTANNO-000163-0001</t>
-  </si>
-  <si>
-    <t>I wish I could go back in time to see history up close.</t>
-  </si>
-  <si>
-    <t>It's sad that we can't go back and witness history firsthand.</t>
-  </si>
-  <si>
-    <t>I understand the desire to experience history firsthand.</t>
-  </si>
-  <si>
-    <t>I understand your sentiment, but it's important to respect the timeline.</t>
-  </si>
-  <si>
-    <t>It's a bittersweet feeling, wanting to experience history firsthand.</t>
-  </si>
-  <si>
-    <t>I know what you mean, it would be amazing to witness some of the most important events in history.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000102-0001</t>
-  </si>
-  <si>
-    <t>The new Pokemon game is such a cash grab. They're releasing the same version with only minor updates.</t>
-  </si>
-  <si>
-    <t>I can't believe they're taking advantage of their fans like that.</t>
-  </si>
-  <si>
-    <t>I know, it's so frustrating.</t>
-  </si>
-  <si>
-    <t>I completely agree, it's a money-making scheme.</t>
-  </si>
-  <si>
-    <t>I completely understand your frustration.</t>
-  </si>
-  <si>
-    <t>It's so frustrating when they do that.</t>
+    <t>SFTANNO-000105-0001</t>
+  </si>
+  <si>
+    <t>I don't like this cold and gloomy weather.</t>
+  </si>
+  <si>
+    <t>I completely understand, it's so depressing.</t>
+  </si>
+  <si>
+    <t>I know, it's so depressing.</t>
+  </si>
+  <si>
+    <t>I know, it's really depressing.</t>
+  </si>
+  <si>
+    <t>Me neither, it makes me feel so unmotivated.</t>
+  </si>
+  <si>
+    <t>I know, it's hard to stay motivated in this weather.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000154-0001</t>
+  </si>
+  <si>
+    <t>My partner keeps criticizing how I chop vegetables, it's driving me insane.</t>
+  </si>
+  <si>
+    <t>Ugh, I hate when people criticize our cooking methods.</t>
+  </si>
+  <si>
+    <t>That's so frustrating, they should be more supportive.</t>
+  </si>
+  <si>
+    <t>That's so frustrating, it's not your fault if they can't cut their own veggies.</t>
+  </si>
+  <si>
+    <t>That's so frustrating, everyone has their own way of doing things.</t>
+  </si>
+  <si>
+    <t>That's frustrating, they should trust your skills in the kitchen.</t>
   </si>
   <si>
     <t>SFTANNO-000011-0001</t>
@@ -476,25 +476,25 @@
     <t>It's such a difficult balance.</t>
   </si>
   <si>
-    <t>SFTANNO-000062-0001</t>
-  </si>
-  <si>
-    <t>I'm thrilled to see more young people engaging in politics.</t>
-  </si>
-  <si>
-    <t>It's inspiring!</t>
-  </si>
-  <si>
-    <t>It's a positive development.</t>
-  </si>
-  <si>
-    <t>That's fantastic!</t>
-  </si>
-  <si>
-    <t>It's a positive trend!</t>
-  </si>
-  <si>
-    <t>It's great to see their enthusiasm.</t>
+    <t>SFTANNO-000118-0001</t>
+  </si>
+  <si>
+    <t>We can support local community clinics and increase our involvement in community-based programs that advocate for health equity.</t>
+  </si>
+  <si>
+    <t>Yes, these initiatives are crucial in promoting health equity and ensuring that everyone has access to quality healthcare.</t>
+  </si>
+  <si>
+    <t>That's a fantastic idea! It's great to see people coming together to make a positive impact on the healthcare system.</t>
+  </si>
+  <si>
+    <t>That's a fantastic idea, and it's uplifting to know that we can make a difference in our own community.</t>
+  </si>
+  <si>
+    <t>That's a fantastic idea! It's wonderful to see people taking an active role in promoting health equity.</t>
+  </si>
+  <si>
+    <t>That's a fantastic idea! We can work towards creating a more inclusive healthcare system by supporting these initiatives.</t>
   </si>
 </sst>
 </file>
@@ -862,14 +862,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" style="2" customWidth="1"/>
-    <col min="2" max="13" width="27.44140625" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
+    <col min="2" max="13" width="27.42578125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -910,7 +910,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -933,22 +933,22 @@
         <v>17</v>
       </c>
       <c r="H2" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -965,19 +965,19 @@
         <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J3" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
@@ -986,7 +986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -997,34 +997,34 @@
         <v>29</v>
       </c>
       <c r="D4" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H4" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="L4" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>36</v>
       </c>
       <c r="D5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
@@ -1053,16 +1053,16 @@
         <v>39</v>
       </c>
       <c r="J5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="L5" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1073,19 +1073,19 @@
         <v>43</v>
       </c>
       <c r="D6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="H6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
@@ -1100,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1111,34 +1111,34 @@
         <v>50</v>
       </c>
       <c r="D7" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J7" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L7" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1155,13 +1155,13 @@
         <v>58</v>
       </c>
       <c r="F8" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
       <c r="H8" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>60</v>
@@ -1173,10 +1173,10 @@
         <v>61</v>
       </c>
       <c r="L8" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -1187,25 +1187,25 @@
         <v>64</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F9" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>68</v>
@@ -1214,7 +1214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
@@ -1225,25 +1225,25 @@
         <v>71</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F10" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H10" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>75</v>
@@ -1252,7 +1252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -1263,34 +1263,34 @@
         <v>78</v>
       </c>
       <c r="D11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>81</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="L11" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>83</v>
       </c>
@@ -1307,28 +1307,28 @@
         <v>86</v>
       </c>
       <c r="F12" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="H12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="L12" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
@@ -1339,34 +1339,34 @@
         <v>92</v>
       </c>
       <c r="D13" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>93</v>
       </c>
       <c r="F13" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>94</v>
       </c>
       <c r="H13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>95</v>
       </c>
       <c r="J13" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>96</v>
       </c>
       <c r="L13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -1377,34 +1377,34 @@
         <v>99</v>
       </c>
       <c r="D14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>101</v>
       </c>
       <c r="H14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>102</v>
       </c>
       <c r="J14" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>103</v>
       </c>
       <c r="L14" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>104</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>107</v>
       </c>
       <c r="F15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>108</v>
@@ -1433,7 +1433,7 @@
         <v>109</v>
       </c>
       <c r="J15" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>110</v>
@@ -1442,7 +1442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -1453,34 +1453,34 @@
         <v>113</v>
       </c>
       <c r="D16" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>115</v>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>116</v>
       </c>
       <c r="J16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>117</v>
       </c>
       <c r="L16" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
@@ -1497,19 +1497,19 @@
         <v>121</v>
       </c>
       <c r="F17" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>122</v>
       </c>
       <c r="H17" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>123</v>
       </c>
       <c r="J17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>124</v>
@@ -1518,7 +1518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>125</v>
       </c>
@@ -1529,34 +1529,34 @@
         <v>127</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>128</v>
       </c>
       <c r="F18" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>129</v>
       </c>
       <c r="H18" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>130</v>
       </c>
       <c r="J18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>131</v>
       </c>
       <c r="L18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>132</v>
       </c>
@@ -1573,28 +1573,28 @@
         <v>135</v>
       </c>
       <c r="F19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>136</v>
       </c>
       <c r="H19" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>137</v>
       </c>
       <c r="J19" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>138</v>
       </c>
       <c r="L19" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>139</v>
       </c>
@@ -1605,34 +1605,34 @@
         <v>141</v>
       </c>
       <c r="D20" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F20" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>143</v>
       </c>
       <c r="H20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J20" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>145</v>
       </c>
       <c r="L20" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>146</v>
       </c>
@@ -1643,13 +1643,13 @@
         <v>148</v>
       </c>
       <c r="D21" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F21" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>150</v>
@@ -1661,16 +1661,16 @@
         <v>151</v>
       </c>
       <c r="J21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L21" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>153</v>
       </c>
@@ -1681,36 +1681,36 @@
         <v>155</v>
       </c>
       <c r="D22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>156</v>
       </c>
       <c r="F22" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H22" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>158</v>
       </c>
       <c r="J22" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>159</v>
       </c>
       <c r="L22" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{694CE50C-044B-4EE2-BFA4-3C74C7E80DF5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{266B148C-F1A9-469E-AAC0-7C3D5F1A6E36}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
